--- a/output/pdf_financials_xlsx/GSR.xlsx
+++ b/output/pdf_financials_xlsx/GSR.xlsx
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.267978</v>
       </c>
     </row>
     <row r="93">
@@ -2836,7 +2836,11 @@
           <t>Reserves 10 8,254,978</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSR.xlsx
+++ b/output/pdf_financials_xlsx/GSR.xlsx
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000279</v>
       </c>
     </row>
     <row r="35">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.000479</v>
       </c>
     </row>
     <row r="37">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010318</v>
+        <v>0.010039</v>
       </c>
     </row>
     <row r="49">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSR.xlsx
+++ b/output/pdf_financials_xlsx/GSR.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.064667</v>
+        <v>0.07166699999999999</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.407056</v>
+        <v>0.422556</v>
       </c>
     </row>
     <row r="8">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.064667</v>
+        <v>0.07166699999999999</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.407056</v>
+        <v>0.422556</v>
       </c>
     </row>
     <row r="11">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="115">
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.39043</v>
       </c>
     </row>
     <row r="116">
@@ -3336,7 +3336,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3362,7 +3366,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -3444,7 +3452,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>1.81935</v>
       </c>
@@ -3878,7 +3890,11 @@
           <t>Director fees 12 11,500 2,000</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.007</v>
       </c>
